--- a/project/HW4/22127435/22127435_BugReport.xlsx
+++ b/project/HW4/22127435/22127435_BugReport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\viett\OneDrive\Documents\GitHub\Testing-PRJ-SM\project\HW4\22127435\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC4FAC7-A407-4D27-9447-CCC49F91FC59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E838C59-AC98-4BF3-9FCE-1DE529175C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="81">
   <si>
     <t>Tester</t>
   </si>
@@ -952,6 +952,69 @@
   <si>
     <t>There is no defects due to platform difference.</t>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">Steps to Reproduce: 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">1. Navigate to home page on the website. 
+2. Observe the header navigation bar and look up for user account.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Expected Result:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> Username will be displayed on behalf of the user's account.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t>Actual Result:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve"> "User Data not found" is displayed.</t>
+    </r>
+  </si>
+  <si>
+    <t>Usename is not displayed, "User Data not found" is displayed instead</t>
+  </si>
+  <si>
+    <t>B011</t>
+  </si>
 </sst>
 </file>
 
@@ -993,7 +1056,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1026,8 +1089,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor rgb="FFDBE5F1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FFB8CCE4"/>
       </patternFill>
     </fill>
   </fills>
@@ -1092,21 +1167,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1119,19 +1182,31 @@
     <xf numFmtId="14" fontId="1" fillId="4" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1359,27 +1434,27 @@
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="5"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="10"/>
     </row>
     <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="11">
         <v>45860</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="5"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="10"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -2373,7 +2448,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Z1001"/>
+  <dimension ref="A1:Z1002"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.109375" customWidth="1"/>
@@ -2389,31 +2464,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="3" t="s">
         <v>11</v>
       </c>
       <c r="J1" s="2"/>
@@ -2435,17 +2510,17 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -2465,31 +2540,31 @@
       <c r="Z2" s="2"/>
     </row>
     <row r="3" spans="1:26" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="5">
         <v>45859</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="J3" s="2"/>
@@ -2511,31 +2586,31 @@
       <c r="Z3" s="2"/>
     </row>
     <row r="4" spans="1:26" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="7">
         <v>45859</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="J4" s="2"/>
@@ -2557,31 +2632,31 @@
       <c r="Z4" s="2"/>
     </row>
     <row r="5" spans="1:26" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="10" t="s">
+      <c r="F5" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="5">
         <v>45859</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="4" t="s">
         <v>29</v>
       </c>
       <c r="J5" s="2"/>
@@ -2603,31 +2678,31 @@
       <c r="Z5" s="2"/>
     </row>
     <row r="6" spans="1:26" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G6" s="13">
+      <c r="G6" s="7">
         <v>45859</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="6" t="s">
         <v>33</v>
       </c>
       <c r="J6" s="2"/>
@@ -2649,31 +2724,31 @@
       <c r="Z6" s="2"/>
     </row>
     <row r="7" spans="1:26" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="5">
         <v>45859</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="4" t="s">
         <v>37</v>
       </c>
       <c r="J7" s="2"/>
@@ -2695,31 +2770,31 @@
       <c r="Z7" s="2"/>
     </row>
     <row r="8" spans="1:26" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D8" s="12" t="s">
+      <c r="D8" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="7">
         <v>45859</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="6" t="s">
         <v>41</v>
       </c>
       <c r="J8" s="2"/>
@@ -2741,31 +2816,31 @@
       <c r="Z8" s="2"/>
     </row>
     <row r="9" spans="1:26" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="5">
         <v>45859</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="4" t="s">
         <v>46</v>
       </c>
       <c r="J9" s="2"/>
@@ -2787,31 +2862,31 @@
       <c r="Z9" s="2"/>
     </row>
     <row r="10" spans="1:26" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="12" t="s">
+      <c r="B10" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="7">
         <v>45859</v>
       </c>
-      <c r="H10" s="12" t="s">
+      <c r="H10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I10" s="6" t="s">
         <v>50</v>
       </c>
       <c r="J10" s="2"/>
@@ -2833,31 +2908,31 @@
       <c r="Z10" s="2"/>
     </row>
     <row r="11" spans="1:26" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F11" s="10" t="s">
+      <c r="F11" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="5">
         <v>45859</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="10" t="s">
+      <c r="I11" s="4" t="s">
         <v>54</v>
       </c>
       <c r="J11" s="2"/>
@@ -2879,31 +2954,31 @@
       <c r="Z11" s="2"/>
     </row>
     <row r="12" spans="1:26" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
+      <c r="A12" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="12" t="s">
+      <c r="C12" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="7">
         <v>45859</v>
       </c>
-      <c r="H12" s="12" t="s">
+      <c r="H12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I12" s="12" t="s">
+      <c r="I12" s="6" t="s">
         <v>58</v>
       </c>
       <c r="J12" s="2"/>
@@ -2924,18 +2999,34 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
-        <v>59</v>
+    <row r="13" spans="1:26" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
+        <v>80</v>
       </c>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="9"/>
+      <c r="B13" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5">
+        <v>45859</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>19</v>
+      </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
@@ -2954,34 +3045,18 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>13</v>
+    <row r="14" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="16" t="s">
+        <v>59</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" s="13">
-        <v>45859</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>63</v>
-      </c>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
@@ -3000,33 +3075,33 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="10" t="s">
-        <v>20</v>
+    <row r="15" spans="1:26" ht="144" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
+        <v>13</v>
       </c>
-      <c r="B15" s="10" t="s">
-        <v>64</v>
+      <c r="B15" s="6" t="s">
+        <v>60</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>65</v>
+      <c r="C15" s="6" t="s">
+        <v>61</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F15" s="10" t="s">
+      <c r="F15" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="7">
         <v>45859</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="10" t="s">
-        <v>66</v>
+      <c r="I15" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -3046,33 +3121,33 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>25</v>
+    <row r="16" spans="1:26" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
+        <v>20</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>67</v>
+      <c r="B16" s="4" t="s">
+        <v>64</v>
       </c>
-      <c r="C16" s="12" t="s">
-        <v>68</v>
+      <c r="C16" s="4" t="s">
+        <v>65</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="12" t="s">
-        <v>28</v>
+      <c r="E16" s="4" t="s">
+        <v>17</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G16" s="13">
+      <c r="G16" s="5">
         <v>45859</v>
       </c>
-      <c r="H16" s="12" t="s">
+      <c r="H16" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I16" s="12" t="s">
-        <v>69</v>
+      <c r="I16" s="4" t="s">
+        <v>66</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -3092,33 +3167,33 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="10" t="s">
-        <v>30</v>
+    <row r="17" spans="1:26" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
+        <v>25</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>70</v>
+      <c r="B17" s="6" t="s">
+        <v>67</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>71</v>
+      <c r="C17" s="6" t="s">
+        <v>68</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>23</v>
+      <c r="E17" s="6" t="s">
+        <v>28</v>
       </c>
-      <c r="F17" s="10" t="s">
+      <c r="F17" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="7">
         <v>45859</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I17" s="10" t="s">
-        <v>72</v>
+      <c r="I17" s="6" t="s">
+        <v>69</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -3138,33 +3213,33 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>34</v>
+    <row r="18" spans="1:26" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="4" t="s">
+        <v>30</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>73</v>
+      <c r="B18" s="4" t="s">
+        <v>70</v>
       </c>
-      <c r="C18" s="12" t="s">
-        <v>74</v>
+      <c r="C18" s="4" t="s">
+        <v>71</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="5">
         <v>45859</v>
       </c>
-      <c r="H18" s="12" t="s">
+      <c r="H18" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="I18" s="12" t="s">
-        <v>75</v>
+      <c r="I18" s="4" t="s">
+        <v>72</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3184,18 +3259,34 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="15" t="s">
-        <v>76</v>
+    <row r="19" spans="1:26" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>34</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
+      <c r="B19" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="7">
+        <v>45859</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>75</v>
+      </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
@@ -3216,7 +3307,7 @@
     </row>
     <row r="20" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -3245,15 +3336,17 @@
       <c r="Z20" s="2"/>
     </row>
     <row r="21" spans="1:26" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="2"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
+      <c r="A21" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -30712,12 +30805,23 @@
       <c r="Y1001" s="2"/>
       <c r="Z1001" s="2"/>
     </row>
+    <row r="1002" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1002" s="2"/>
+      <c r="B1002" s="2"/>
+      <c r="C1002" s="2"/>
+      <c r="D1002" s="2"/>
+      <c r="E1002" s="2"/>
+      <c r="F1002" s="2"/>
+      <c r="G1002" s="2"/>
+      <c r="H1002" s="2"/>
+      <c r="I1002" s="2"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:I2"/>
-    <mergeCell ref="A13:I13"/>
-    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A14:I14"/>
     <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A21:I21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
